--- a/data/trans_orig/P37A$medicoenfermedad-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P37A$medicoenfermedad-Provincia-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>8715</t>
+          <t>8164</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>23027</t>
+          <t>22627</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,43%</t>
+          <t>8,29%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1736</t>
+          <t>1603</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>10403</t>
+          <t>10506</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>11693</t>
+          <t>11504</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>28636</t>
+          <t>28355</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,31%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>249983</t>
+          <t>250383</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>264295</t>
+          <t>264846</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>91,57%</t>
+          <t>91,71%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,81%</t>
+          <t>97,01%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>250435</t>
+          <t>250332</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>259102</t>
+          <t>259235</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,01%</t>
+          <t>95,97%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,33%</t>
+          <t>99,39%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>505493</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>522155</t>
+          <t>522344</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,64%</t>
+          <t>94,69%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,81%</t>
+          <t>97,85%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>11939</t>
+          <t>11275</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>28729</t>
+          <t>29183</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,82 +1091,82 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
+          <t>2,29%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>5,92%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>14587</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>8716</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>23739</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>2,89%</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>1,73%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>4,71%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>33810</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>24117</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>45515</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>3,39%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
           <t>2,42%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>5,83%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>14587</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>8266</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>22407</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>2,89%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>1,64%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>4,45%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>33810</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>23597</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>47127</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>3,39%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>2,37%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,57%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>464346</t>
+          <t>463892</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>481136</t>
+          <t>481800</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,82 +1204,82 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,17%</t>
+          <t>94,08%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
+          <t>97,71%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>484</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>489362</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>480210</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>495233</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>97,11%</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>95,29%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>98,27%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>930</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>963214</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>951509</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>972907</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>96,61%</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>95,43%</t>
+        </is>
+      </c>
+      <c r="W8" s="2" t="inlineStr">
+        <is>
           <t>97,58%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>484</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>489362</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>481542</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>495683</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>97,11%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>95,55%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>98,36%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>930</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>963214</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>949897</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>973427</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>96,61%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>95,27%</t>
-        </is>
-      </c>
-      <c r="W8" s="2" t="inlineStr">
-        <is>
-          <t>97,63%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>8669</t>
+          <t>7967</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>23582</t>
+          <t>24310</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1011</t>
+          <t>1001</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>10264</t>
+          <t>10667</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>10732</t>
+          <t>11468</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>28407</t>
+          <t>29015</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,43%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>295264</t>
+          <t>294536</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>310177</t>
+          <t>310879</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>92,6%</t>
+          <t>92,38%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,28%</t>
+          <t>97,5%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>325148</t>
+          <t>324745</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>334401</t>
+          <t>334411</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,94%</t>
+          <t>96,82%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>625851</t>
+          <t>625243</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>643526</t>
+          <t>642790</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,66%</t>
+          <t>95,57%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,36%</t>
+          <t>98,25%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2887</t>
+          <t>2804</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>13163</t>
+          <t>13146</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,7 +1777,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>10223</t>
+          <t>10421</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>25757</t>
+          <t>25300</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>6,81%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>15546</t>
+          <t>15233</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>35065</t>
+          <t>34554</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,73%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>345508</t>
+          <t>345525</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>355784</t>
+          <t>355867</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1895,7 +1895,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,2%</t>
+          <t>99,22%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>345699</t>
+          <t>346156</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>361233</t>
+          <t>361035</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,07%</t>
+          <t>93,19%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,25%</t>
+          <t>97,19%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>695062</t>
+          <t>695573</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>714581</t>
+          <t>714894</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,2%</t>
+          <t>95,27%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,87%</t>
+          <t>97,91%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4513</t>
+          <t>4958</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>17423</t>
+          <t>17579</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>8,65%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>7058</t>
+          <t>6421</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>21149</t>
+          <t>20696</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>10,18%</t>
+          <t>9,97%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>14042</t>
+          <t>14215</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>33822</t>
+          <t>34003</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>8,27%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>185885</t>
+          <t>185729</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>198795</t>
+          <t>198350</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>91,43%</t>
+          <t>91,35%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,78%</t>
+          <t>97,56%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>186519</t>
+          <t>186972</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>200610</t>
+          <t>201247</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>89,82%</t>
+          <t>90,03%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>96,6%</t>
+          <t>96,91%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>377154</t>
+          <t>376973</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>396934</t>
+          <t>396761</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>91,77%</t>
+          <t>91,73%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,58%</t>
+          <t>96,54%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2908</t>
+          <t>2921</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>14120</t>
+          <t>14174</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1982</t>
+          <t>1934</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>11369</t>
+          <t>11110</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>6897</t>
+          <t>6904</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>20867</t>
+          <t>20244</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,69%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>256691</t>
+          <t>256637</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>267903</t>
+          <t>267890</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>94,79%</t>
+          <t>94,77%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,93%</t>
+          <t>98,92%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>266775</t>
+          <t>267034</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>276162</t>
+          <t>276210</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>95,91%</t>
+          <t>96,01%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>99,29%</t>
+          <t>99,3%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>528088</t>
+          <t>528711</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>542058</t>
+          <t>542051</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>96,2%</t>
+          <t>96,31%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>11304</t>
+          <t>11312</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>29170</t>
+          <t>28168</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2811,7 +2811,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>6361</t>
+          <t>6531</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>21054</t>
+          <t>21505</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>21258</t>
+          <t>22427</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>43363</t>
+          <t>45283</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,61%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>585857</t>
+          <t>586859</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>603723</t>
+          <t>603715</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,7 +2919,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>95,26%</t>
+          <t>95,42%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>617165</t>
+          <t>616714</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>631858</t>
+          <t>631688</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>96,7%</t>
+          <t>96,63%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,0%</t>
+          <t>98,98%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1209883</t>
+          <t>1207963</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1231988</t>
+          <t>1230819</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>96,54%</t>
+          <t>96,39%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>98,3%</t>
+          <t>98,21%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>14989</t>
+          <t>15010</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>33991</t>
+          <t>35424</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3154,7 +3154,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>14934</t>
+          <t>15209</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>35767</t>
+          <t>34721</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>35615</t>
+          <t>35392</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>62063</t>
+          <t>62154</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,07%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>709804</t>
+          <t>708371</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>728806</t>
+          <t>728785</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,7 +3262,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>95,43%</t>
+          <t>95,24%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>747744</t>
+          <t>748790</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>768577</t>
+          <t>768302</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>95,44%</t>
+          <t>95,57%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>98,09%</t>
+          <t>98,06%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1465243</t>
+          <t>1465152</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1491691</t>
+          <t>1491914</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>95,94%</t>
+          <t>95,93%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>97,67%</t>
+          <t>97,68%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>92818</t>
+          <t>93850</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>134187</t>
+          <t>134078</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>76264</t>
+          <t>75676</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>114793</t>
+          <t>112191</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>180170</t>
+          <t>179404</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>236111</t>
+          <t>232890</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,5%</t>
         </is>
       </c>
     </row>
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3142356</t>
+          <t>3142465</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3183725</t>
+          <t>3182693</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>95,9%</t>
+          <t>95,91%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>97,17%</t>
+          <t>97,14%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3264404</t>
+          <t>3267006</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3302933</t>
+          <t>3303521</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>96,6%</t>
+          <t>96,68%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>97,74%</t>
+          <t>97,76%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6419630</t>
+          <t>6422851</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6475571</t>
+          <t>6476337</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3675,12 +3675,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>96,45%</t>
+          <t>96,5%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>97,29%</t>
+          <t>97,3%</t>
         </is>
       </c>
     </row>
@@ -4056,12 +4056,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3475</t>
+          <t>3473</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>14998</t>
+          <t>14372</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4076,7 +4076,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3045</t>
+          <t>3077</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>14238</t>
+          <t>14351</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>8933</t>
+          <t>8499</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>23975</t>
+          <t>24058</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,13%</t>
         </is>
       </c>
     </row>
@@ -4169,12 +4169,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>279740</t>
+          <t>280366</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>291263</t>
+          <t>291265</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4184,7 +4184,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,91%</t>
+          <t>95,12%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>273007</t>
+          <t>272894</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>284200</t>
+          <t>284168</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,04%</t>
+          <t>95,0%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,94%</t>
+          <t>98,93%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>558008</t>
+          <t>557925</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>573050</t>
+          <t>573484</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,88%</t>
+          <t>95,87%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,47%</t>
+          <t>98,54%</t>
         </is>
       </c>
     </row>
@@ -4399,12 +4399,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>14835</t>
+          <t>15153</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>36944</t>
+          <t>36751</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>18900</t>
+          <t>19794</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>38809</t>
+          <t>41614</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>7,95%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>38835</t>
+          <t>37548</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>69027</t>
+          <t>69098</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4484,7 +4484,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -4512,12 +4512,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>468583</t>
+          <t>468776</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>490692</t>
+          <t>490374</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>92,69%</t>
+          <t>92,73%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,07%</t>
+          <t>97,0%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>484956</t>
+          <t>482151</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>504865</t>
+          <t>503971</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,59%</t>
+          <t>92,05%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,39%</t>
+          <t>96,22%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>960265</t>
+          <t>960194</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>990457</t>
+          <t>991744</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4602,7 +4602,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,23%</t>
+          <t>96,35%</t>
         </is>
       </c>
     </row>
@@ -4742,12 +4742,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5259</t>
+          <t>4911</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>19960</t>
+          <t>18639</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4135</t>
+          <t>5093</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>18901</t>
+          <t>19449</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4792,12 +4792,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>12289</t>
+          <t>12480</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>32694</t>
+          <t>31851</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>4,79%</t>
         </is>
       </c>
     </row>
@@ -4855,12 +4855,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>304086</t>
+          <t>305407</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>318787</t>
+          <t>319135</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4870,12 +4870,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,84%</t>
+          <t>94,25%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,38%</t>
+          <t>98,48%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>322119</t>
+          <t>321571</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>336885</t>
+          <t>335927</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4905,12 +4905,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,46%</t>
+          <t>94,3%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,79%</t>
+          <t>98,51%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>632372</t>
+          <t>633215</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>652777</t>
+          <t>652586</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4940,12 +4940,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,08%</t>
+          <t>95,21%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,15%</t>
+          <t>98,12%</t>
         </is>
       </c>
     </row>
@@ -5085,12 +5085,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8186</t>
+          <t>8209</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>25709</t>
+          <t>24694</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5105,7 +5105,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>10103</t>
+          <t>11001</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>26527</t>
+          <t>27917</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>7,18%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>22163</t>
+          <t>21699</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>44914</t>
+          <t>44386</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5170,12 +5170,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>5,82%</t>
         </is>
       </c>
     </row>
@@ -5198,12 +5198,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>348273</t>
+          <t>349288</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>365796</t>
+          <t>365773</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5213,7 +5213,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,13%</t>
+          <t>93,4%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>362424</t>
+          <t>361034</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>378848</t>
+          <t>377950</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,18%</t>
+          <t>92,82%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,4%</t>
+          <t>97,17%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>718019</t>
+          <t>718547</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>740770</t>
+          <t>741234</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5283,12 +5283,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,11%</t>
+          <t>94,18%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,1%</t>
+          <t>97,16%</t>
         </is>
       </c>
     </row>
@@ -5428,12 +5428,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3329</t>
+          <t>3207</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>15265</t>
+          <t>14330</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5443,12 +5443,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>8199</t>
+          <t>8112</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>23051</t>
+          <t>23490</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5498,12 +5498,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>13908</t>
+          <t>14820</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>33152</t>
+          <t>32782</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5513,12 +5513,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>7,58%</t>
         </is>
       </c>
     </row>
@@ -5541,12 +5541,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>197353</t>
+          <t>198288</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>209289</t>
+          <t>209411</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>92,82%</t>
+          <t>93,26%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,43%</t>
+          <t>98,49%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>196540</t>
+          <t>196101</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>211392</t>
+          <t>211479</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>89,5%</t>
+          <t>89,3%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>96,27%</t>
+          <t>96,31%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>399057</t>
+          <t>399427</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>418301</t>
+          <t>417389</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>92,33%</t>
+          <t>92,42%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,78%</t>
+          <t>96,57%</t>
         </is>
       </c>
     </row>
@@ -5771,12 +5771,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>6241</t>
+          <t>6248</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>19827</t>
+          <t>20064</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5791,7 +5791,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>8055</t>
+          <t>8234</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>23591</t>
+          <t>23374</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>8,35%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>16879</t>
+          <t>16841</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>37061</t>
+          <t>36620</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5856,12 +5856,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>6,61%</t>
         </is>
       </c>
     </row>
@@ -5884,12 +5884,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>254154</t>
+          <t>253917</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>267740</t>
+          <t>267733</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5899,7 +5899,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>92,76%</t>
+          <t>92,68%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>256440</t>
+          <t>256657</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>271976</t>
+          <t>271797</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>91,58%</t>
+          <t>91,65%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>97,12%</t>
+          <t>97,06%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>516951</t>
+          <t>517392</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>537133</t>
+          <t>537171</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5969,12 +5969,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>93,31%</t>
+          <t>93,39%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>96,95%</t>
+          <t>96,96%</t>
         </is>
       </c>
     </row>
@@ -6114,12 +6114,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>15717</t>
+          <t>15738</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>35505</t>
+          <t>36151</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6134,7 +6134,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>20614</t>
+          <t>20217</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>42632</t>
+          <t>43807</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>6,31%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>40091</t>
+          <t>40414</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>71518</t>
+          <t>69646</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6199,12 +6199,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>5,13%</t>
         </is>
       </c>
     </row>
@@ -6227,12 +6227,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>627283</t>
+          <t>626637</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>647071</t>
+          <t>647050</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6242,7 +6242,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>94,64%</t>
+          <t>94,55%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>651221</t>
+          <t>650046</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>673239</t>
+          <t>673636</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>93,86%</t>
+          <t>93,69%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>97,03%</t>
+          <t>97,09%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1285123</t>
+          <t>1286995</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1316550</t>
+          <t>1316227</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6312,12 +6312,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>94,73%</t>
+          <t>94,87%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>97,04%</t>
+          <t>97,02%</t>
         </is>
       </c>
     </row>
@@ -6457,12 +6457,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>16139</t>
+          <t>15947</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>38211</t>
+          <t>37191</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>11943</t>
+          <t>11562</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>31066</t>
+          <t>29570</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>32559</t>
+          <t>31006</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>61612</t>
+          <t>60599</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,78%</t>
         </is>
       </c>
     </row>
@@ -6570,12 +6570,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>740887</t>
+          <t>741907</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>762959</t>
+          <t>763151</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>95,1%</t>
+          <t>95,23%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>97,93%</t>
+          <t>97,95%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>792787</t>
+          <t>794283</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>811910</t>
+          <t>812291</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>96,23%</t>
+          <t>96,41%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>98,55%</t>
+          <t>98,6%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6640,12 +6640,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1541339</t>
+          <t>1542352</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1570392</t>
+          <t>1571945</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6655,12 +6655,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>96,16%</t>
+          <t>96,22%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>97,97%</t>
+          <t>98,07%</t>
         </is>
       </c>
     </row>
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>104290</t>
+          <t>104014</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>149818</t>
+          <t>153414</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6820,77 +6820,77 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
+          <t>4,48%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>132</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>141406</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>116341</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>164928</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>3,97%</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>3,27%</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>4,64%</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr">
+        <is>
+          <t>245</t>
+        </is>
+      </c>
+      <c r="R28" s="2" t="inlineStr">
+        <is>
+          <t>266564</t>
+        </is>
+      </c>
+      <c r="S28" s="2" t="inlineStr">
+        <is>
+          <t>234629</t>
+        </is>
+      </c>
+      <c r="T28" s="2" t="inlineStr">
+        <is>
+          <t>305274</t>
+        </is>
+      </c>
+      <c r="U28" s="2" t="inlineStr">
+        <is>
+          <t>3,82%</t>
+        </is>
+      </c>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
+          <t>3,36%</t>
+        </is>
+      </c>
+      <c r="W28" s="2" t="inlineStr">
+        <is>
           <t>4,37%</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>132</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="inlineStr">
-        <is>
-          <t>141406</t>
-        </is>
-      </c>
-      <c r="L28" s="2" t="inlineStr">
-        <is>
-          <t>119979</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="inlineStr">
-        <is>
-          <t>166399</t>
-        </is>
-      </c>
-      <c r="N28" s="2" t="inlineStr">
-        <is>
-          <t>3,97%</t>
-        </is>
-      </c>
-      <c r="O28" s="2" t="inlineStr">
-        <is>
-          <t>3,37%</t>
-        </is>
-      </c>
-      <c r="P28" s="2" t="inlineStr">
-        <is>
-          <t>4,68%</t>
-        </is>
-      </c>
-      <c r="Q28" s="2" t="inlineStr">
-        <is>
-          <t>245</t>
-        </is>
-      </c>
-      <c r="R28" s="2" t="inlineStr">
-        <is>
-          <t>266564</t>
-        </is>
-      </c>
-      <c r="S28" s="2" t="inlineStr">
-        <is>
-          <t>236250</t>
-        </is>
-      </c>
-      <c r="T28" s="2" t="inlineStr">
-        <is>
-          <t>304336</t>
-        </is>
-      </c>
-      <c r="U28" s="2" t="inlineStr">
-        <is>
-          <t>3,82%</t>
-        </is>
-      </c>
-      <c r="V28" s="2" t="inlineStr">
-        <is>
-          <t>3,38%</t>
-        </is>
-      </c>
-      <c r="W28" s="2" t="inlineStr">
-        <is>
-          <t>4,36%</t>
         </is>
       </c>
     </row>
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3276961</t>
+          <t>3273365</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3322489</t>
+          <t>3322765</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6928,82 +6928,82 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
+          <t>95,52%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>96,96%</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>3166</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>3416903</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>3393381</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>3441968</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>96,03%</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>95,36%</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>96,73%</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr">
+        <is>
+          <t>6262</t>
+        </is>
+      </c>
+      <c r="R29" s="2" t="inlineStr">
+        <is>
+          <t>6718524</t>
+        </is>
+      </c>
+      <c r="S29" s="2" t="inlineStr">
+        <is>
+          <t>6679814</t>
+        </is>
+      </c>
+      <c r="T29" s="2" t="inlineStr">
+        <is>
+          <t>6750459</t>
+        </is>
+      </c>
+      <c r="U29" s="2" t="inlineStr">
+        <is>
+          <t>96,18%</t>
+        </is>
+      </c>
+      <c r="V29" s="2" t="inlineStr">
+        <is>
           <t>95,63%</t>
         </is>
       </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>96,96%</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>3166</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t>3416903</t>
-        </is>
-      </c>
-      <c r="L29" s="2" t="inlineStr">
-        <is>
-          <t>3391910</t>
-        </is>
-      </c>
-      <c r="M29" s="2" t="inlineStr">
-        <is>
-          <t>3438330</t>
-        </is>
-      </c>
-      <c r="N29" s="2" t="inlineStr">
-        <is>
-          <t>96,03%</t>
-        </is>
-      </c>
-      <c r="O29" s="2" t="inlineStr">
-        <is>
-          <t>95,32%</t>
-        </is>
-      </c>
-      <c r="P29" s="2" t="inlineStr">
-        <is>
-          <t>96,63%</t>
-        </is>
-      </c>
-      <c r="Q29" s="2" t="inlineStr">
-        <is>
-          <t>6262</t>
-        </is>
-      </c>
-      <c r="R29" s="2" t="inlineStr">
-        <is>
-          <t>6718524</t>
-        </is>
-      </c>
-      <c r="S29" s="2" t="inlineStr">
-        <is>
-          <t>6680752</t>
-        </is>
-      </c>
-      <c r="T29" s="2" t="inlineStr">
-        <is>
-          <t>6748838</t>
-        </is>
-      </c>
-      <c r="U29" s="2" t="inlineStr">
-        <is>
-          <t>96,18%</t>
-        </is>
-      </c>
-      <c r="V29" s="2" t="inlineStr">
-        <is>
-          <t>95,64%</t>
-        </is>
-      </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>96,62%</t>
+          <t>96,64%</t>
         </is>
       </c>
     </row>
@@ -7379,12 +7379,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>8886</t>
+          <t>9021</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>26995</t>
+          <t>26445</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7394,12 +7394,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,19%</t>
+          <t>9,0%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5377</t>
+          <t>5196</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>19525</t>
+          <t>17695</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7429,12 +7429,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>17915</t>
+          <t>17420</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>38795</t>
+          <t>39149</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>6,72%</t>
         </is>
       </c>
     </row>
@@ -7492,12 +7492,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>266766</t>
+          <t>267316</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>284875</t>
+          <t>284740</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7507,12 +7507,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>90,81%</t>
+          <t>91,0%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,97%</t>
+          <t>96,93%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>269178</t>
+          <t>271008</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>283326</t>
+          <t>283507</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7542,12 +7542,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,24%</t>
+          <t>93,87%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,14%</t>
+          <t>98,2%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>543669</t>
+          <t>543315</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>564549</t>
+          <t>565044</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,34%</t>
+          <t>93,28%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,92%</t>
+          <t>97,01%</t>
         </is>
       </c>
     </row>
@@ -7722,12 +7722,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>17475</t>
+          <t>16774</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>40263</t>
+          <t>39366</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7737,12 +7737,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>7,83%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>9956</t>
+          <t>9957</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>26452</t>
+          <t>26765</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7777,7 +7777,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>31097</t>
+          <t>30705</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>56818</t>
+          <t>56875</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,55%</t>
         </is>
       </c>
     </row>
@@ -7835,12 +7835,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>462312</t>
+          <t>463209</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>485100</t>
+          <t>485801</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7850,12 +7850,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>91,99%</t>
+          <t>92,17%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,52%</t>
+          <t>96,66%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>496632</t>
+          <t>496319</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>513128</t>
+          <t>513127</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7885,7 +7885,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,94%</t>
+          <t>94,88%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>968841</t>
+          <t>968784</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>994562</t>
+          <t>994954</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,46%</t>
+          <t>94,45%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,97%</t>
+          <t>97,01%</t>
         </is>
       </c>
     </row>
@@ -8065,12 +8065,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5660</t>
+          <t>5226</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>17743</t>
+          <t>18201</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8080,12 +8080,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4933</t>
+          <t>4962</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>18152</t>
+          <t>18598</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8115,12 +8115,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8135,12 +8135,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>13149</t>
+          <t>11877</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>31221</t>
+          <t>30619</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8150,12 +8150,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,68%</t>
         </is>
       </c>
     </row>
@@ -8178,12 +8178,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>300822</t>
+          <t>300364</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>312905</t>
+          <t>313339</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,43%</t>
+          <t>94,29%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,22%</t>
+          <t>98,36%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>318157</t>
+          <t>317711</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>331376</t>
+          <t>331347</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8228,12 +8228,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,6%</t>
+          <t>94,47%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,53%</t>
+          <t>98,52%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8248,12 +8248,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>623653</t>
+          <t>624255</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>641725</t>
+          <t>642997</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8263,12 +8263,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,23%</t>
+          <t>95,32%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,99%</t>
+          <t>98,19%</t>
         </is>
       </c>
     </row>
@@ -8408,12 +8408,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>15837</t>
+          <t>16051</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>34667</t>
+          <t>34806</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,37%</t>
+          <t>9,41%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8443,12 +8443,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>17918</t>
+          <t>18745</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>39276</t>
+          <t>39824</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8458,12 +8458,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,14%</t>
+          <t>10,28%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8478,12 +8478,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>37098</t>
+          <t>38388</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>66722</t>
+          <t>69184</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8493,12 +8493,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>9,14%</t>
         </is>
       </c>
     </row>
@@ -8521,12 +8521,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>335297</t>
+          <t>335158</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>354127</t>
+          <t>353913</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>90,63%</t>
+          <t>90,59%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,72%</t>
+          <t>95,66%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8556,12 +8556,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>348007</t>
+          <t>347459</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>369365</t>
+          <t>368538</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8571,12 +8571,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>89,86%</t>
+          <t>89,72%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,37%</t>
+          <t>95,16%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>690525</t>
+          <t>688063</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>720149</t>
+          <t>718859</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,19%</t>
+          <t>90,86%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,1%</t>
+          <t>94,93%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2572</t>
+          <t>2566</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>13744</t>
+          <t>13762</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>6,52%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1123</t>
+          <t>1125</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>11227</t>
+          <t>9708</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8806,7 +8806,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>5206</t>
+          <t>5474</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>20189</t>
+          <t>19394</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,51%</t>
         </is>
       </c>
     </row>
@@ -8864,12 +8864,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>197477</t>
+          <t>197459</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>208649</t>
+          <t>208655</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>93,49%</t>
+          <t>93,48%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,78%</t>
+          <t>98,79%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>207360</t>
+          <t>208879</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>217464</t>
+          <t>217462</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8914,7 +8914,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>94,86%</t>
+          <t>95,56%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -8934,12 +8934,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>409619</t>
+          <t>410414</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>424602</t>
+          <t>424334</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8949,12 +8949,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,3%</t>
+          <t>95,49%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,79%</t>
+          <t>98,73%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2486</t>
+          <t>2580</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>13782</t>
+          <t>12701</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1011</t>
+          <t>1012</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>10418</t>
+          <t>9481</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9149,7 +9149,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>4937</t>
+          <t>4936</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>17724</t>
+          <t>18407</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9184,7 +9184,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,43%</t>
         </is>
       </c>
     </row>
@@ -9207,12 +9207,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>249341</t>
+          <t>250422</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>260637</t>
+          <t>260543</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9222,12 +9222,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>94,76%</t>
+          <t>95,17%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,06%</t>
+          <t>99,02%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>262697</t>
+          <t>263634</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>272104</t>
+          <t>272103</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9257,7 +9257,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>96,19%</t>
+          <t>96,53%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>518514</t>
+          <t>517831</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>531301</t>
+          <t>531302</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9292,7 +9292,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>96,69%</t>
+          <t>96,57%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>8543</t>
+          <t>8594</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>24010</t>
+          <t>24458</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>10946</t>
+          <t>10569</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>27332</t>
+          <t>27657</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>23974</t>
+          <t>24165</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>46369</t>
+          <t>45931</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,41%</t>
         </is>
       </c>
     </row>
@@ -9550,12 +9550,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>632548</t>
+          <t>632100</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>648015</t>
+          <t>647964</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9565,12 +9565,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>96,34%</t>
+          <t>96,27%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,7%</t>
+          <t>98,69%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9585,12 +9585,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>663962</t>
+          <t>663637</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>680348</t>
+          <t>680725</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9600,12 +9600,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>96,05%</t>
+          <t>96,0%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>98,42%</t>
+          <t>98,47%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1301483</t>
+          <t>1301921</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1323878</t>
+          <t>1323687</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9635,12 +9635,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>96,56%</t>
+          <t>96,59%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>98,22%</t>
+          <t>98,21%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>7216</t>
+          <t>7125</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>21949</t>
+          <t>22142</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>9484</t>
+          <t>8592</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>27135</t>
+          <t>27104</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9830,7 +9830,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>19709</t>
+          <t>19789</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>41880</t>
+          <t>42496</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9870,7 +9870,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,65%</t>
         </is>
       </c>
     </row>
@@ -9893,12 +9893,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>756634</t>
+          <t>756441</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>771367</t>
+          <t>771458</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9908,12 +9908,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>97,18%</t>
+          <t>97,16%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>99,07%</t>
+          <t>99,08%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>799032</t>
+          <t>799063</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>816683</t>
+          <t>817575</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9948,7 +9948,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>98,85%</t>
+          <t>98,96%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1562870</t>
+          <t>1562254</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1585041</t>
+          <t>1584961</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9978,7 +9978,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>97,39%</t>
+          <t>97,35%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>97872</t>
+          <t>97222</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>140840</t>
+          <t>140278</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>86925</t>
+          <t>86840</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>129041</t>
+          <t>130473</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10178,7 +10178,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>197047</t>
+          <t>198917</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>254881</t>
+          <t>256454</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,7%</t>
         </is>
       </c>
     </row>
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3253510</t>
+          <t>3254072</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3296478</t>
+          <t>3297128</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>95,85%</t>
+          <t>95,87%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>97,12%</t>
+          <t>97,14%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3415501</t>
+          <t>3414069</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3457617</t>
+          <t>3457702</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10286,7 +10286,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>96,36%</t>
+          <t>96,32%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6684011</t>
+          <t>6682438</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6741845</t>
+          <t>6739975</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10321,12 +10321,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>96,33%</t>
+          <t>96,3%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>97,16%</t>
+          <t>97,13%</t>
         </is>
       </c>
     </row>
@@ -10697,32 +10697,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>11614</t>
+          <t>12605</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6603</t>
+          <t>7215</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>18823</t>
+          <t>19643</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10732,32 +10732,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>8895</t>
+          <t>9221</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5227</t>
+          <t>5586</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>14054</t>
+          <t>14314</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10767,32 +10767,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>20510</t>
+          <t>21826</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>14416</t>
+          <t>15467</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>29531</t>
+          <t>29854</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>4,7%</t>
         </is>
       </c>
     </row>
@@ -10810,32 +10810,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>299829</t>
+          <t>306240</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>292620</t>
+          <t>299202</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>304840</t>
+          <t>311630</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>96,27%</t>
+          <t>96,05%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,96%</t>
+          <t>93,84%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,88%</t>
+          <t>97,74%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10845,32 +10845,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>280740</t>
+          <t>306840</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>275581</t>
+          <t>301747</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>284408</t>
+          <t>310475</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>96,93%</t>
+          <t>97,08%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,15%</t>
+          <t>95,47%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,2%</t>
+          <t>98,23%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10880,32 +10880,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>580567</t>
+          <t>613080</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>571546</t>
+          <t>605052</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>586661</t>
+          <t>619439</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>96,59%</t>
+          <t>96,56%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,09%</t>
+          <t>95,3%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,6%</t>
+          <t>97,56%</t>
         </is>
       </c>
     </row>
@@ -10923,17 +10923,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -10958,17 +10958,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -10993,17 +10993,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11040,32 +11040,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>17792</t>
+          <t>17885</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10870</t>
+          <t>10803</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>28478</t>
+          <t>28221</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11075,32 +11075,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>15429</t>
+          <t>15543</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>10066</t>
+          <t>10185</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>23668</t>
+          <t>23606</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11110,32 +11110,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>33221</t>
+          <t>33428</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>23936</t>
+          <t>24592</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>45917</t>
+          <t>46969</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,36%</t>
         </is>
       </c>
     </row>
@@ -11153,32 +11153,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>500598</t>
+          <t>512762</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>489912</t>
+          <t>502426</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>507520</t>
+          <t>519844</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>96,57%</t>
+          <t>96,63%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,51%</t>
+          <t>94,68%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,9%</t>
+          <t>97,96%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11188,32 +11188,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>499540</t>
+          <t>530951</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>491301</t>
+          <t>522888</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>504903</t>
+          <t>536309</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>97,0%</t>
+          <t>97,16%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,4%</t>
+          <t>95,68%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,05%</t>
+          <t>98,14%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11223,32 +11223,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>1000138</t>
+          <t>1043713</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>987442</t>
+          <t>1030172</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1009423</t>
+          <t>1052549</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>96,79%</t>
+          <t>96,9%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,56%</t>
+          <t>95,64%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,68%</t>
+          <t>97,72%</t>
         </is>
       </c>
     </row>
@@ -11266,17 +11266,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -11301,17 +11301,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>514969</t>
+          <t>546494</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>514969</t>
+          <t>546494</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>514969</t>
+          <t>546494</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -11336,17 +11336,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1033359</t>
+          <t>1077141</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1033359</t>
+          <t>1077141</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1033359</t>
+          <t>1077141</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -11383,32 +11383,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>13145</t>
+          <t>12887</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7615</t>
+          <t>7871</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>19775</t>
+          <t>19857</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11418,32 +11418,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>12300</t>
+          <t>12315</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>7256</t>
+          <t>7609</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>18808</t>
+          <t>19586</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11453,32 +11453,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>25445</t>
+          <t>25202</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>18053</t>
+          <t>17919</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>35254</t>
+          <t>34644</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,15%</t>
         </is>
       </c>
     </row>
@@ -11496,32 +11496,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>302905</t>
+          <t>303106</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>296275</t>
+          <t>296136</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>308435</t>
+          <t>308122</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>95,84%</t>
+          <t>95,92%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,74%</t>
+          <t>93,72%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,59%</t>
+          <t>97,51%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11531,32 +11531,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>336828</t>
+          <t>344066</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>330320</t>
+          <t>336795</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>341872</t>
+          <t>348772</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>96,48%</t>
+          <t>96,54%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,61%</t>
+          <t>94,5%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,92%</t>
+          <t>97,86%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11566,32 +11566,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>639733</t>
+          <t>647173</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>629924</t>
+          <t>637731</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>647125</t>
+          <t>654456</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>96,17%</t>
+          <t>96,25%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,7%</t>
+          <t>94,85%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,29%</t>
+          <t>97,33%</t>
         </is>
       </c>
     </row>
@@ -11609,17 +11609,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -11644,17 +11644,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -11679,17 +11679,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>665178</t>
+          <t>672375</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>665178</t>
+          <t>672375</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>665178</t>
+          <t>672375</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -11726,32 +11726,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>21577</t>
+          <t>22675</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>13071</t>
+          <t>13617</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>35103</t>
+          <t>36313</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,23%</t>
+          <t>9,73%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11761,32 +11761,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>28815</t>
+          <t>31239</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>17722</t>
+          <t>23957</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>42065</t>
+          <t>44903</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>10,64%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11796,32 +11796,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>50392</t>
+          <t>53915</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>34857</t>
+          <t>43048</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>69575</t>
+          <t>70870</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>6,78%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>8,91%</t>
         </is>
       </c>
     </row>
@@ -11839,32 +11839,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>290980</t>
+          <t>350470</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>277454</t>
+          <t>336832</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>299486</t>
+          <t>359528</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>93,1%</t>
+          <t>93,92%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>88,77%</t>
+          <t>90,27%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,82%</t>
+          <t>96,35%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11874,32 +11874,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>446903</t>
+          <t>390722</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>433653</t>
+          <t>377058</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>457996</t>
+          <t>398004</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>93,94%</t>
+          <t>92,6%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,16%</t>
+          <t>89,36%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,27%</t>
+          <t>94,32%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11909,32 +11909,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>737882</t>
+          <t>741192</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>718699</t>
+          <t>724237</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>753417</t>
+          <t>752059</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>93,61%</t>
+          <t>93,22%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,17%</t>
+          <t>91,09%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,58%</t>
+          <t>94,59%</t>
         </is>
       </c>
     </row>
@@ -11952,17 +11952,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -11987,17 +11987,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -12022,17 +12022,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -12069,32 +12069,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>14642</t>
+          <t>15789</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>9862</t>
+          <t>10384</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>21317</t>
+          <t>22451</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>8,19%</t>
+          <t>7,68%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>11,93%</t>
+          <t>10,92%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12104,32 +12104,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>23752</t>
+          <t>25107</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>12464</t>
+          <t>19346</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>32388</t>
+          <t>31580</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>9,18%</t>
+          <t>10,97%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>8,45%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>12,52%</t>
+          <t>13,8%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12139,32 +12139,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>38394</t>
+          <t>40896</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>26373</t>
+          <t>32606</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>48083</t>
+          <t>49845</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>8,78%</t>
+          <t>9,41%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>7,5%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>10,99%</t>
+          <t>11,47%</t>
         </is>
       </c>
     </row>
@@ -12182,32 +12182,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>164100</t>
+          <t>189876</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>157425</t>
+          <t>183214</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>168880</t>
+          <t>195281</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>91,81%</t>
+          <t>92,32%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>88,07%</t>
+          <t>89,08%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>94,48%</t>
+          <t>94,95%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12217,32 +12217,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>235027</t>
+          <t>203811</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>226391</t>
+          <t>197338</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>246315</t>
+          <t>209572</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>90,82%</t>
+          <t>89,03%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>87,48%</t>
+          <t>86,2%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>95,18%</t>
+          <t>91,55%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12252,32 +12252,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>399127</t>
+          <t>393686</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>389438</t>
+          <t>384737</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>411148</t>
+          <t>401976</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>91,22%</t>
+          <t>90,59%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>89,01%</t>
+          <t>88,53%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>93,97%</t>
+          <t>92,5%</t>
         </is>
       </c>
     </row>
@@ -12295,17 +12295,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -12330,17 +12330,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>258779</t>
+          <t>228918</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>258779</t>
+          <t>228918</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>258779</t>
+          <t>228918</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -12365,17 +12365,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>437521</t>
+          <t>434582</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>437521</t>
+          <t>434582</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>437521</t>
+          <t>434582</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -12412,32 +12412,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>10364</t>
+          <t>10151</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>6275</t>
+          <t>6353</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>16435</t>
+          <t>17067</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12447,22 +12447,22 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>6593</t>
+          <t>6992</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>3669</t>
+          <t>3770</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>11022</t>
+          <t>11891</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
@@ -12472,7 +12472,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12482,32 +12482,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>16957</t>
+          <t>17143</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>11144</t>
+          <t>11925</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>24646</t>
+          <t>24436</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,57%</t>
         </is>
       </c>
     </row>
@@ -12525,32 +12525,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>259272</t>
+          <t>260556</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>253201</t>
+          <t>253640</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>263361</t>
+          <t>264354</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>96,16%</t>
+          <t>96,25%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>93,9%</t>
+          <t>93,7%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>97,67%</t>
+          <t>97,65%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12560,27 +12560,27 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>250463</t>
+          <t>256758</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>246034</t>
+          <t>251859</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>253387</t>
+          <t>259980</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>97,44%</t>
+          <t>97,35%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>95,71%</t>
+          <t>95,49%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -12595,32 +12595,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>509735</t>
+          <t>517314</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>502046</t>
+          <t>510021</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>515548</t>
+          <t>522532</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>96,78%</t>
+          <t>96,79%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>95,32%</t>
+          <t>95,43%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>97,88%</t>
+          <t>97,77%</t>
         </is>
       </c>
     </row>
@@ -12638,17 +12638,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -12673,17 +12673,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -12708,17 +12708,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -12755,32 +12755,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>46799</t>
+          <t>54240</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>35413</t>
+          <t>41137</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>60652</t>
+          <t>70506</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>9,72%</t>
+          <t>9,8%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12790,32 +12790,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>50688</t>
+          <t>62750</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>24434</t>
+          <t>51253</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>71838</t>
+          <t>77053</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>8,13%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>9,98%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12825,32 +12825,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>97487</t>
+          <t>116990</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>61349</t>
+          <t>100310</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>121899</t>
+          <t>137581</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>7,84%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>9,22%</t>
         </is>
       </c>
     </row>
@@ -12868,32 +12868,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>577480</t>
+          <t>665447</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>563627</t>
+          <t>649181</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>588866</t>
+          <t>678550</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>92,5%</t>
+          <t>92,46%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>90,28%</t>
+          <t>90,2%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>94,33%</t>
+          <t>94,28%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12903,32 +12903,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>798577</t>
+          <t>709307</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>777427</t>
+          <t>695004</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>824831</t>
+          <t>720804</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>94,03%</t>
+          <t>91,87%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>91,54%</t>
+          <t>90,02%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>97,12%</t>
+          <t>93,36%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12938,32 +12938,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1376057</t>
+          <t>1374754</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1351645</t>
+          <t>1354163</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1412195</t>
+          <t>1391434</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>93,38%</t>
+          <t>92,16%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>91,73%</t>
+          <t>90,78%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>95,84%</t>
+          <t>93,28%</t>
         </is>
       </c>
     </row>
@@ -12981,17 +12981,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>624279</t>
+          <t>719687</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>624279</t>
+          <t>719687</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>624279</t>
+          <t>719687</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13016,17 +13016,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>849265</t>
+          <t>772057</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>849265</t>
+          <t>772057</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>849265</t>
+          <t>772057</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13051,17 +13051,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>1473544</t>
+          <t>1491744</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1473544</t>
+          <t>1491744</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1473544</t>
+          <t>1491744</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -13098,32 +13098,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>45061</t>
+          <t>50871</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>19161</t>
+          <t>38918</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>66335</t>
+          <t>65228</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>8,17%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13133,27 +13133,27 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>64307</t>
+          <t>73123</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>52410</t>
+          <t>61467</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>76209</t>
+          <t>88277</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>8,96%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>7,39%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -13168,32 +13168,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>109369</t>
+          <t>123994</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>67168</t>
+          <t>106864</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>135601</t>
+          <t>145124</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>7,61%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>6,56%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>8,24%</t>
+          <t>8,91%</t>
         </is>
       </c>
     </row>
@@ -13211,32 +13211,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>883659</t>
+          <t>747201</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>862385</t>
+          <t>732844</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>909559</t>
+          <t>759154</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>95,15%</t>
+          <t>93,63%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>92,86%</t>
+          <t>91,83%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>97,94%</t>
+          <t>95,12%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13246,22 +13246,22 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>653424</t>
+          <t>758208</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>641522</t>
+          <t>743054</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>665321</t>
+          <t>769864</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>91,04%</t>
+          <t>91,2%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
@@ -13271,7 +13271,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>92,7%</t>
+          <t>92,61%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13281,32 +13281,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>1537083</t>
+          <t>1505409</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1510851</t>
+          <t>1484279</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1579284</t>
+          <t>1522539</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>93,36%</t>
+          <t>92,39%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>91,76%</t>
+          <t>91,09%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>95,92%</t>
+          <t>93,44%</t>
         </is>
       </c>
     </row>
@@ -13324,17 +13324,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -13359,17 +13359,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>717731</t>
+          <t>831331</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>717731</t>
+          <t>831331</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>717731</t>
+          <t>831331</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -13394,17 +13394,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>1646452</t>
+          <t>1629403</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1646452</t>
+          <t>1629403</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1646452</t>
+          <t>1629403</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -13441,32 +13441,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>180994</t>
+          <t>197102</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>144690</t>
+          <t>174010</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>213009</t>
+          <t>226084</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13476,32 +13476,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>210781</t>
+          <t>236290</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>172014</t>
+          <t>213731</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>238691</t>
+          <t>260319</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>6,32%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,97%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13511,32 +13511,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>391775</t>
+          <t>433392</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>340406</t>
+          <t>402625</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>436642</t>
+          <t>471890</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>6,49%</t>
         </is>
       </c>
     </row>
@@ -13554,32 +13554,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>3278823</t>
+          <t>3335660</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3246808</t>
+          <t>3306678</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3315127</t>
+          <t>3358752</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>94,77%</t>
+          <t>94,42%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>93,84%</t>
+          <t>93,6%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>95,82%</t>
+          <t>95,07%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13589,32 +13589,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>3501499</t>
+          <t>3500664</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3473589</t>
+          <t>3476635</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3540266</t>
+          <t>3523223</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>94,32%</t>
+          <t>93,68%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>93,57%</t>
+          <t>93,03%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>95,37%</t>
+          <t>94,28%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13624,32 +13624,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>6780322</t>
+          <t>6836324</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6735455</t>
+          <t>6797826</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6831691</t>
+          <t>6867091</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>94,54%</t>
+          <t>94,04%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>93,91%</t>
+          <t>93,51%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>95,25%</t>
+          <t>94,46%</t>
         </is>
       </c>
     </row>
@@ -13667,17 +13667,17 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -13702,17 +13702,17 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -13737,17 +13737,17 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
